--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_181_R19.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_181_R19.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Y. FALL</t>
+          <t>D. BRIZUELA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.6449</v>
+        <v>3.8562</v>
       </c>
       <c r="E2" t="n">
-        <v>4.8769</v>
+        <v>4.9064</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.232</v>
+        <v>-1.0502</v>
       </c>
       <c r="G2" t="n">
-        <v>3.1403</v>
+        <v>2.1167</v>
       </c>
       <c r="H2" t="n">
-        <v>3.7526</v>
+        <v>4.9876</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.6122</v>
+        <v>-2.8709</v>
       </c>
       <c r="J2" t="n">
-        <v>3.1153</v>
+        <v>3.9754</v>
       </c>
       <c r="K2" t="n">
-        <v>3.0417</v>
+        <v>5.3173</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0736</v>
+        <v>-1.3419</v>
       </c>
       <c r="M2" t="n">
-        <v>0.025</v>
+        <v>-1.8587</v>
       </c>
       <c r="N2" t="n">
-        <v>0.7109</v>
+        <v>-0.3298</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.6859</v>
+        <v>-1.529</v>
       </c>
       <c r="P2" t="n">
-        <v>1.3917</v>
+        <v>1.6237</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.3917</v>
+        <v>1.6237</v>
       </c>
       <c r="S2" t="n">
-        <v>1.7212</v>
+        <v>-0.9564</v>
       </c>
       <c r="T2" t="n">
-        <v>1.7616</v>
+        <v>-0.1412</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.0404</v>
+        <v>-0.8151</v>
       </c>
       <c r="V2" t="n">
-        <v>-1.6083</v>
+        <v>1.0722</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.6083</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M. NORRIS</t>
+          <t>Y. FALL</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.1395</v>
+        <v>3.1025</v>
       </c>
       <c r="E3" t="n">
-        <v>2.6575</v>
+        <v>3.5362</v>
       </c>
       <c r="F3" t="n">
-        <v>0.482</v>
+        <v>-0.4336</v>
       </c>
       <c r="G3" t="n">
-        <v>2.1218</v>
+        <v>3.1403</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.4043</v>
+        <v>3.7526</v>
       </c>
       <c r="I3" t="n">
-        <v>2.5261</v>
+        <v>-0.6122</v>
       </c>
       <c r="J3" t="n">
-        <v>3.066</v>
+        <v>3.1153</v>
       </c>
       <c r="K3" t="n">
-        <v>0.2724</v>
+        <v>3.0417</v>
       </c>
       <c r="L3" t="n">
-        <v>2.7937</v>
+        <v>0.0736</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.9442</v>
+        <v>0.025</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.6766</v>
+        <v>0.7109</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.2676</v>
+        <v>-0.6859</v>
       </c>
       <c r="P3" t="n">
-        <v>1.6237</v>
+        <v>1.3917</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.232</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.8556</v>
+        <v>1.3917</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.3224</v>
+        <v>0.1788</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.1766</v>
+        <v>0.4208</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1458</v>
+        <v>-0.242</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.2836</v>
+        <v>-1.6083</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.2836</v>
+        <v>-1.6083</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>D. BRIZUELA</t>
+          <t>M. NORRIS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.9565</v>
+        <v>2.9036</v>
       </c>
       <c r="E4" t="n">
-        <v>4.2419</v>
+        <v>2.4216</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.2854</v>
+        <v>0.482</v>
       </c>
       <c r="G4" t="n">
-        <v>2.1167</v>
+        <v>2.1218</v>
       </c>
       <c r="H4" t="n">
-        <v>4.9876</v>
+        <v>-0.4043</v>
       </c>
       <c r="I4" t="n">
-        <v>-2.8709</v>
+        <v>2.5261</v>
       </c>
       <c r="J4" t="n">
-        <v>3.9754</v>
+        <v>3.066</v>
       </c>
       <c r="K4" t="n">
-        <v>5.3173</v>
+        <v>0.2724</v>
       </c>
       <c r="L4" t="n">
-        <v>-1.3419</v>
+        <v>2.7937</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.8587</v>
+        <v>-0.9442</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.3298</v>
+        <v>-0.6766</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.529</v>
+        <v>-0.2676</v>
       </c>
       <c r="P4" t="n">
         <v>1.6237</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-0.232</v>
       </c>
       <c r="R4" t="n">
-        <v>1.6237</v>
+        <v>1.8556</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.856</v>
+        <v>-0.5583</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.8057</v>
+        <v>-0.4125</v>
       </c>
       <c r="U4" t="n">
-        <v>-1.0504</v>
+        <v>-0.1458</v>
       </c>
       <c r="V4" t="n">
-        <v>1.0722</v>
+        <v>-0.2836</v>
       </c>
       <c r="W4" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-0.2836</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.4448</v>
+        <v>2.1753</v>
       </c>
       <c r="E5" t="n">
-        <v>1.602</v>
+        <v>1.3661</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8427</v>
+        <v>0.8091</v>
       </c>
       <c r="G5" t="n">
         <v>2.5419</v>
@@ -844,13 +844,13 @@
         <v>1.6237</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.329</v>
+        <v>-0.5985</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1845</v>
+        <v>-0.4204</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1445</v>
+        <v>-0.1781</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0873</v>
+        <v>-0.0979</v>
       </c>
       <c r="E6" t="n">
-        <v>0.5923</v>
+        <v>0.4743</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.505</v>
+        <v>-0.5722</v>
       </c>
       <c r="G6" t="n">
         <v>-0.7159</v>
@@ -922,13 +922,13 @@
         <v>1.1598</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0378</v>
+        <v>-0.1474</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0474</v>
+        <v>-0.07049999999999999</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0097</v>
+        <v>-0.0769</v>
       </c>
       <c r="V6" t="n">
         <v>-0.3943</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2</v>
+        <v>-1.8991</v>
       </c>
       <c r="E7" t="n">
         <v>-1.3626</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.6373</v>
+        <v>-0.5365</v>
       </c>
       <c r="G7" t="n">
         <v>-1.5286</v>
@@ -1000,13 +1000,13 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2394</v>
+        <v>-0.1386</v>
       </c>
       <c r="T7" t="n">
         <v>-0.1494</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0901</v>
+        <v>0.0108</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>T. SATORANSKY</t>
+          <t>J. PARRA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.7711</v>
+        <v>-3.5255</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.1449</v>
+        <v>-2.2441</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.6262</v>
+        <v>-1.2813</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.7282999999999999</v>
+        <v>-3.4561</v>
       </c>
       <c r="H8" t="n">
-        <v>1.209</v>
+        <v>-0.4848</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.9373</v>
+        <v>-2.9713</v>
       </c>
       <c r="J8" t="n">
-        <v>0.3512</v>
+        <v>-2.2014</v>
       </c>
       <c r="K8" t="n">
-        <v>0.7093</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.3581</v>
+        <v>-2.2854</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.0795</v>
+        <v>-1.2547</v>
       </c>
       <c r="N8" t="n">
-        <v>0.4997</v>
+        <v>-0.5688</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.5792</v>
+        <v>-0.6859</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.6959</v>
+        <v>0.9278</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.3195</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.6237</v>
+        <v>0.9278</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.2025</v>
+        <v>-0.0668</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1766</v>
+        <v>-0.1845</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0259</v>
+        <v>0.1177</v>
       </c>
       <c r="V8" t="n">
-        <v>-2.1444</v>
+        <v>-0.9304</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.1418</v>
       </c>
       <c r="X8" t="n">
-        <v>-2.1444</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. PARRA</t>
+          <t>T. SATORANSKY</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.8031</v>
+        <v>-3.7465</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.7906</v>
+        <v>-1.9523</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.0125</v>
+        <v>-1.7942</v>
       </c>
       <c r="G9" t="n">
-        <v>-3.4561</v>
+        <v>-0.7282999999999999</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.4848</v>
+        <v>1.209</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.9713</v>
+        <v>-1.9373</v>
       </c>
       <c r="J9" t="n">
-        <v>-2.2014</v>
+        <v>0.3512</v>
       </c>
       <c r="K9" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.7093</v>
       </c>
       <c r="L9" t="n">
-        <v>-2.2854</v>
+        <v>-0.3581</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.2547</v>
+        <v>-1.0795</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.5688</v>
+        <v>0.4997</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.6859</v>
+        <v>-1.5792</v>
       </c>
       <c r="P9" t="n">
-        <v>0.9278</v>
+        <v>-0.6959</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-2.3195</v>
       </c>
       <c r="R9" t="n">
-        <v>0.9278</v>
+        <v>1.6237</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3444</v>
+        <v>-0.1779</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.731</v>
+        <v>0.016</v>
       </c>
       <c r="U9" t="n">
-        <v>0.3866</v>
+        <v>-0.1939</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.9304</v>
+        <v>-2.1444</v>
       </c>
       <c r="W9" t="n">
-        <v>0.1418</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.0722</v>
+        <v>-2.1444</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.8244</v>
+        <v>-3.7571</v>
       </c>
       <c r="E10" t="n">
         <v>-2.714</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.1104</v>
+        <v>-1.0432</v>
       </c>
       <c r="G10" t="n">
         <v>-1.019</v>
@@ -1234,13 +1234,13 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2539</v>
+        <v>-0.1867</v>
       </c>
       <c r="T10" t="n">
         <v>-0.2161</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0378</v>
+        <v>0.0294</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.9134</v>
+        <v>-4.4759</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.2495</v>
+        <v>-4.0136</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.6639</v>
+        <v>-0.4622</v>
       </c>
       <c r="G11" t="n">
         <v>-4.752</v>
@@ -1312,13 +1312,13 @@
         <v>0.4639</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.5377</v>
+        <v>-0.1002</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.5895</v>
+        <v>-0.3536</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0518</v>
+        <v>0.2535</v>
       </c>
       <c r="V11" t="n">
         <v>1.0722</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-7.2684</v>
+        <v>-6.4696</v>
       </c>
       <c r="E12" t="n">
-        <v>-7.147</v>
+        <v>-6.4826</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.1214</v>
+        <v>0.013</v>
       </c>
       <c r="G12" t="n">
         <v>-5.7083</v>
@@ -1390,13 +1390,13 @@
         <v>2.0876</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.9391</v>
+        <v>-1.1402</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.0376</v>
+        <v>-0.3732</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.9014</v>
+        <v>-0.767</v>
       </c>
       <c r="V12" t="n">
         <v>2.0026</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-12.3074</v>
+        <v>-11.934</v>
       </c>
       <c r="E13" t="n">
-        <v>-6.438</v>
+        <v>-6.0646</v>
       </c>
       <c r="F13" t="n">
-        <v>-5.869400000000001</v>
+        <v>-5.869299999999999</v>
       </c>
       <c r="G13" t="n">
         <v>-7.987500000000001</v>
@@ -1468,13 +1468,13 @@
         <v>12.7575</v>
       </c>
       <c r="S13" t="n">
-        <v>-4.2654</v>
+        <v>-3.8922</v>
       </c>
       <c r="T13" t="n">
-        <v>-2.258</v>
+        <v>-1.8846</v>
       </c>
       <c r="U13" t="n">
-        <v>-2.0076</v>
+        <v>-2.0074</v>
       </c>
       <c r="V13" t="n">
         <v>-1.214</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>7.4277</v>
+        <v>6.4777</v>
       </c>
       <c r="E14" t="n">
-        <v>7.0106</v>
+        <v>5.4772</v>
       </c>
       <c r="F14" t="n">
-        <v>0.4171</v>
+        <v>1.0005</v>
       </c>
       <c r="G14" t="n">
         <v>2.4971</v>
@@ -1546,13 +1546,13 @@
         <v>1.6237</v>
       </c>
       <c r="S14" t="n">
-        <v>2.4873</v>
+        <v>1.5373</v>
       </c>
       <c r="T14" t="n">
-        <v>2.4065</v>
+        <v>0.8731</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0808</v>
+        <v>0.6642</v>
       </c>
       <c r="V14" t="n">
         <v>0.8197</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.7467</v>
+        <v>3.2914</v>
       </c>
       <c r="E15" t="n">
-        <v>1.5188</v>
+        <v>1.8727</v>
       </c>
       <c r="F15" t="n">
-        <v>1.2278</v>
+        <v>1.4187</v>
       </c>
       <c r="G15" t="n">
         <v>-0.4976</v>
@@ -1624,13 +1624,13 @@
         <v>1.8556</v>
       </c>
       <c r="S15" t="n">
-        <v>0.2623</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.0114</v>
+        <v>0.3424</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2737</v>
+        <v>0.4646</v>
       </c>
       <c r="V15" t="n">
         <v>2.2862</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. BLOSSOMGAME</t>
+          <t>N. NEDOVIC</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.4646</v>
+        <v>2.4331</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.5251</v>
+        <v>1.5887</v>
       </c>
       <c r="F16" t="n">
-        <v>2.9897</v>
+        <v>0.8444</v>
       </c>
       <c r="G16" t="n">
-        <v>0.7829</v>
+        <v>2.0421</v>
       </c>
       <c r="H16" t="n">
-        <v>0.4382</v>
+        <v>-0.0491</v>
       </c>
       <c r="I16" t="n">
-        <v>0.3447</v>
+        <v>2.0912</v>
       </c>
       <c r="J16" t="n">
-        <v>0.0645</v>
+        <v>1.8885</v>
       </c>
       <c r="K16" t="n">
-        <v>0.1883</v>
+        <v>0.3193</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.1239</v>
+        <v>1.5692</v>
       </c>
       <c r="M16" t="n">
-        <v>0.7184</v>
+        <v>0.1536</v>
       </c>
       <c r="N16" t="n">
-        <v>0.2499</v>
+        <v>-0.3684</v>
       </c>
       <c r="O16" t="n">
-        <v>0.4685</v>
+        <v>0.5221</v>
       </c>
       <c r="P16" t="n">
-        <v>1.6237</v>
+        <v>-0.6959</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R16" t="n">
-        <v>1.6237</v>
+        <v>0.4639</v>
       </c>
       <c r="S16" t="n">
-        <v>0.1999</v>
+        <v>0.0147</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.5895</v>
+        <v>-0.2122</v>
       </c>
       <c r="U16" t="n">
-        <v>0.7894</v>
+        <v>0.2269</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.1418</v>
+        <v>1.0722</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.1418</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>N. MIROTIC</t>
+          <t>J. BLOSSOMGAME</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.1885</v>
+        <v>2.4209</v>
       </c>
       <c r="E17" t="n">
-        <v>2.5428</v>
+        <v>-0.2892</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.3543</v>
+        <v>2.7101</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.2718</v>
+        <v>0.7829</v>
       </c>
       <c r="H17" t="n">
-        <v>-2.3061</v>
+        <v>0.4382</v>
       </c>
       <c r="I17" t="n">
-        <v>2.0343</v>
+        <v>0.3447</v>
       </c>
       <c r="J17" t="n">
-        <v>1.0157</v>
+        <v>0.0645</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.3929</v>
+        <v>0.1883</v>
       </c>
       <c r="L17" t="n">
-        <v>1.4085</v>
+        <v>-0.1239</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.2874</v>
+        <v>0.7184</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.9132</v>
+        <v>0.2499</v>
       </c>
       <c r="O17" t="n">
-        <v>0.6258</v>
+        <v>0.4685</v>
       </c>
       <c r="P17" t="n">
-        <v>0.6959</v>
+        <v>1.6237</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.6959</v>
+        <v>1.6237</v>
       </c>
       <c r="S17" t="n">
-        <v>1.2283</v>
+        <v>0.1562</v>
       </c>
       <c r="T17" t="n">
-        <v>0.9911</v>
+        <v>-0.3536</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2372</v>
+        <v>0.5098</v>
       </c>
       <c r="V17" t="n">
-        <v>0.5361</v>
+        <v>-0.1418</v>
       </c>
       <c r="W17" t="n">
-        <v>0.5361</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>N. NEDOVIC</t>
+          <t>N. MIROTIC</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.9392</v>
+        <v>2.177</v>
       </c>
       <c r="E18" t="n">
-        <v>1.3528</v>
+        <v>2.3069</v>
       </c>
       <c r="F18" t="n">
-        <v>0.5863</v>
+        <v>-0.1299</v>
       </c>
       <c r="G18" t="n">
-        <v>2.0421</v>
+        <v>-0.2718</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.0491</v>
+        <v>-2.3061</v>
       </c>
       <c r="I18" t="n">
-        <v>2.0912</v>
+        <v>2.0343</v>
       </c>
       <c r="J18" t="n">
-        <v>1.8885</v>
+        <v>1.0157</v>
       </c>
       <c r="K18" t="n">
-        <v>0.3193</v>
+        <v>-0.3929</v>
       </c>
       <c r="L18" t="n">
-        <v>1.5692</v>
+        <v>1.4085</v>
       </c>
       <c r="M18" t="n">
-        <v>0.1536</v>
+        <v>-1.2874</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.3684</v>
+        <v>-1.9132</v>
       </c>
       <c r="O18" t="n">
-        <v>0.5221</v>
+        <v>0.6258</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.6959</v>
+        <v>0.6959</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.4639</v>
+        <v>0.6959</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.4793</v>
+        <v>1.2169</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.4481</v>
+        <v>0.7551</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0312</v>
+        <v>0.4617</v>
       </c>
       <c r="V18" t="n">
-        <v>1.0722</v>
+        <v>0.5361</v>
       </c>
       <c r="W18" t="n">
-        <v>1.0722</v>
+        <v>0.5361</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.0389</v>
+        <v>1.1969</v>
       </c>
       <c r="E19" t="n">
-        <v>0.0493</v>
+        <v>0.2852</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9896</v>
+        <v>0.9116</v>
       </c>
       <c r="G19" t="n">
         <v>0.217</v>
@@ -1936,13 +1936,13 @@
         <v>0.4639</v>
       </c>
       <c r="S19" t="n">
-        <v>0.358</v>
+        <v>0.516</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.0747</v>
+        <v>0.1612</v>
       </c>
       <c r="U19" t="n">
-        <v>0.4327</v>
+        <v>0.3547</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.9865</v>
+        <v>1.1723</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.006</v>
+        <v>0.3478</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9925</v>
+        <v>0.8245</v>
       </c>
       <c r="G20" t="n">
         <v>2.736</v>
@@ -2014,13 +2014,13 @@
         <v>1.6237</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.06900000000000001</v>
+        <v>0.1169</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.5816</v>
+        <v>-0.2278</v>
       </c>
       <c r="U20" t="n">
-        <v>0.5127</v>
+        <v>0.3446</v>
       </c>
       <c r="V20" t="n">
         <v>-2.1444</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>D. THEIS</t>
+          <t>A. DIALLO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.266</v>
+        <v>-0.4782</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.6298</v>
+        <v>-1.6276</v>
       </c>
       <c r="F21" t="n">
-        <v>0.8959</v>
+        <v>1.1494</v>
       </c>
       <c r="G21" t="n">
-        <v>0.9477</v>
+        <v>1.2589</v>
       </c>
       <c r="H21" t="n">
-        <v>2.1355</v>
+        <v>1.0949</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.1878</v>
+        <v>0.1641</v>
       </c>
       <c r="J21" t="n">
-        <v>0.3866</v>
+        <v>1.4882</v>
       </c>
       <c r="K21" t="n">
-        <v>1.8856</v>
+        <v>2.0537</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.4991</v>
+        <v>-0.5655</v>
       </c>
       <c r="M21" t="n">
-        <v>0.5611</v>
+        <v>-0.2293</v>
       </c>
       <c r="N21" t="n">
-        <v>0.2499</v>
+        <v>-0.9588</v>
       </c>
       <c r="O21" t="n">
-        <v>0.3113</v>
+        <v>0.7296</v>
       </c>
       <c r="P21" t="n">
-        <v>-2.7834</v>
+        <v>-1.6237</v>
       </c>
       <c r="Q21" t="n">
         <v>-3.4793</v>
       </c>
       <c r="R21" t="n">
-        <v>0.6959</v>
+        <v>1.8556</v>
       </c>
       <c r="S21" t="n">
-        <v>1.5657</v>
+        <v>0.4226</v>
       </c>
       <c r="T21" t="n">
-        <v>1.9268</v>
+        <v>-0.1727</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3611</v>
+        <v>0.5953000000000001</v>
       </c>
       <c r="V21" t="n">
-        <v>0.5361</v>
+        <v>-0.5361</v>
       </c>
       <c r="W21" t="n">
         <v>0.5361</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. DIALLO</t>
+          <t>D. THEIS</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.276</v>
+        <v>-0.9477</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.3353</v>
+        <v>-2.0453</v>
       </c>
       <c r="F22" t="n">
-        <v>1.0593</v>
+        <v>1.0975</v>
       </c>
       <c r="G22" t="n">
-        <v>1.2589</v>
+        <v>0.9477</v>
       </c>
       <c r="H22" t="n">
-        <v>1.0949</v>
+        <v>2.1355</v>
       </c>
       <c r="I22" t="n">
-        <v>0.1641</v>
+        <v>-1.1878</v>
       </c>
       <c r="J22" t="n">
-        <v>1.4882</v>
+        <v>0.3866</v>
       </c>
       <c r="K22" t="n">
-        <v>2.0537</v>
+        <v>1.8856</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.5655</v>
+        <v>-1.4991</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.2293</v>
+        <v>0.5611</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.9588</v>
+        <v>0.2499</v>
       </c>
       <c r="O22" t="n">
-        <v>0.7296</v>
+        <v>0.3113</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.6237</v>
+        <v>-2.7834</v>
       </c>
       <c r="Q22" t="n">
         <v>-3.4793</v>
       </c>
       <c r="R22" t="n">
-        <v>1.8556</v>
+        <v>0.6959</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.3752</v>
+        <v>0.3519</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.8804</v>
+        <v>0.5113</v>
       </c>
       <c r="U22" t="n">
-        <v>0.5052</v>
+        <v>-0.1595</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.5361</v>
+        <v>0.5361</v>
       </c>
       <c r="W22" t="n">
         <v>0.5361</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.4747</v>
+        <v>-3.8633</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.1089</v>
+        <v>-2.0473</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.3658</v>
+        <v>-1.816</v>
       </c>
       <c r="G23" t="n">
         <v>-1.7246</v>
@@ -2248,13 +2248,13 @@
         <v>0.6959</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.9124</v>
+        <v>0.6989</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.731</v>
+        <v>0.3306</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1814</v>
+        <v>0.3684</v>
       </c>
       <c r="V23" t="n">
         <v>-1.214</v>
@@ -2281,19 +2281,19 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>12.3074</v>
+        <v>13.8801</v>
       </c>
       <c r="E24" t="n">
-        <v>5.869199999999999</v>
+        <v>5.8691</v>
       </c>
       <c r="F24" t="n">
-        <v>6.4381</v>
+        <v>8.0108</v>
       </c>
       <c r="G24" t="n">
         <v>7.987700000000001</v>
       </c>
       <c r="H24" t="n">
-        <v>-4.6103</v>
+        <v>-4.610299999999999</v>
       </c>
       <c r="I24" t="n">
         <v>12.5977</v>
@@ -2305,7 +2305,7 @@
         <v>3.7065</v>
       </c>
       <c r="L24" t="n">
-        <v>7.126</v>
+        <v>7.125999999999999</v>
       </c>
       <c r="M24" t="n">
         <v>-2.8452</v>
@@ -2314,7 +2314,7 @@
         <v>-8.316599999999999</v>
       </c>
       <c r="O24" t="n">
-        <v>5.471799999999999</v>
+        <v>5.4718</v>
       </c>
       <c r="P24" t="n">
         <v>-1.1597</v>
@@ -2326,19 +2326,19 @@
         <v>11.5978</v>
       </c>
       <c r="S24" t="n">
-        <v>4.265599999999999</v>
+        <v>5.8384</v>
       </c>
       <c r="T24" t="n">
-        <v>2.0077</v>
+        <v>2.0074</v>
       </c>
       <c r="U24" t="n">
-        <v>2.258</v>
+        <v>3.8307</v>
       </c>
       <c r="V24" t="n">
         <v>1.214</v>
       </c>
       <c r="W24" t="n">
-        <v>5.7864</v>
+        <v>5.786400000000001</v>
       </c>
       <c r="X24" t="n">
         <v>-4.5724</v>
